--- a/countries/cn/2026-2029.xlsx
+++ b/countries/cn/2026-2029.xlsx
@@ -50220,7 +50220,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -50451,7 +50451,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -50843,7 +50843,7 @@
       </c>
       <c r="AJ334" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK334" t="inlineStr">
@@ -51239,7 +51239,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -51635,7 +51635,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -52031,7 +52031,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -52427,7 +52427,7 @@
       </c>
       <c r="AJ342" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK342" t="inlineStr">
@@ -59287,7 +59287,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">

--- a/countries/cn/2026-2029.xlsx
+++ b/countries/cn/2026-2029.xlsx
@@ -50220,7 +50220,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -50451,7 +50451,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -50843,7 +50843,7 @@
       </c>
       <c r="AJ334" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK334" t="inlineStr">
@@ -51239,7 +51239,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -51635,7 +51635,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -52031,7 +52031,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -52427,7 +52427,7 @@
       </c>
       <c r="AJ342" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK342" t="inlineStr">
@@ -59287,7 +59287,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">

--- a/countries/cn/2026-2029.xlsx
+++ b/countries/cn/2026-2029.xlsx
@@ -50220,7 +50220,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -50451,7 +50451,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -50843,7 +50843,7 @@
       </c>
       <c r="AJ334" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK334" t="inlineStr">
@@ -51239,7 +51239,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -51635,7 +51635,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -52031,7 +52031,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -52427,7 +52427,7 @@
       </c>
       <c r="AJ342" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK342" t="inlineStr">
@@ -59287,7 +59287,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">

--- a/countries/cn/2026-2029.xlsx
+++ b/countries/cn/2026-2029.xlsx
@@ -50220,7 +50220,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -50451,7 +50451,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -50843,7 +50843,7 @@
       </c>
       <c r="AJ334" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK334" t="inlineStr">
@@ -51239,7 +51239,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -51635,7 +51635,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -52031,7 +52031,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -52427,7 +52427,7 @@
       </c>
       <c r="AJ342" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK342" t="inlineStr">
@@ -59287,7 +59287,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
